--- a/xls/square_20_tri3_17.xlsx
+++ b/xls/square_20_tri3_17.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
+        <v>324</v>
+      </c>
+      <c r="C15" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15">
+        <v>441</v>
+      </c>
+      <c r="E15" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15">
+        <v>256</v>
+      </c>
+      <c r="G15" t="s">
+        <v>13</v>
+      </c>
+      <c r="H15">
+        <v>1350</v>
+      </c>
+      <c r="I15">
+        <v>3.0839227840404018</v>
+      </c>
+      <c r="J15">
+        <v>-0.2569876587904282</v>
+      </c>
+      <c r="K15">
+        <v>0.8693410358165482</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
+        <v>324</v>
+      </c>
+      <c r="C16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16">
+        <v>441</v>
+      </c>
+      <c r="E16" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16">
+        <v>289</v>
+      </c>
+      <c r="G16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16">
+        <v>1536</v>
+      </c>
+      <c r="I16">
+        <v>2.0172788480902346</v>
+      </c>
+      <c r="J16">
+        <v>-0.9975971018436133</v>
+      </c>
+      <c r="K16">
+        <v>0.3003765974900126</v>
+      </c>
+    </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>11</v>
